--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-28).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 541.339,01</t>
-  </si>
-  <si>
-    <t>R$ 3.024,24
-R$ 3.081,45</t>
-  </si>
-  <si>
-    <t>3.0%
-4.6%</t>
-  </si>
-  <si>
-    <t>34.7</t>
-  </si>
-  <si>
-    <t>(1.6%)</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>(40.8%)</t>
-  </si>
-  <si>
-    <t>4.6%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 553.242,41</t>
+  </si>
+  <si>
+    <t>R$ 3.006,75
+R$ 3.061,43</t>
+  </si>
+  <si>
+    <t>3.2%
+4.8%</t>
+  </si>
+  <si>
+    <t>34.5</t>
+  </si>
+  <si>
+    <t>(1.4%)</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>(40.1%)</t>
+  </si>
+  <si>
+    <t>4.7%</t>
   </si>
   <si>
     <t>0.0%</t>
@@ -953,13 +953,13 @@
     <t>76.7%</t>
   </si>
   <si>
-    <t>7.0%</t>
+    <t>6.9%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.2</t>
   </si>
   <si>
     <t>10.9</t>
@@ -968,10 +968,10 @@
     <t>17.6</t>
   </si>
   <si>
-    <t>77.8%</t>
-  </si>
-  <si>
-    <t>-R$ 17.018,83</t>
+    <t>77.9%</t>
+  </si>
+  <si>
+    <t>-R$ 17.360,33</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>5.7265159090909092</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>10.810226999999999</v>
+      </c>
       <c r="AD13" s="8">
         <v>17.384073333333333</v>
       </c>
@@ -5922,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5958,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>4667.3800000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4667.3800000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>1.6442880775942168</v>
+      </c>
+      <c r="R36" s="7">
+        <v>38</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.34663194340293696</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.035110276000668468</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.057265960774567311</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.014674614023285014</v>
+      </c>
+      <c r="X36" s="8">
+        <v>24.830769230769231</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.2092583333333335</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>4.3871807692307687</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>16.489742307692307</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6672,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6708,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2082.0900000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2082.0900000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.14701167345184918</v>
+      </c>
+      <c r="R42" s="7">
+        <v>29</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.093599700301139718</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.18098977469753946</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.084887781027717338</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.019688870317805664</v>
+      </c>
+      <c r="X42" s="8">
+        <v>21.94920476190476</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>4.5047607142857142</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.5214285714285714</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.210316000000001</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.159523809523812</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.90476190476190477</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7807,7 +7879,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7843,25 +7915,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>481.69999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>481.69999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.42612404393719172</v>
+      </c>
+      <c r="R51" s="7">
+        <v>4</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.55555555555555558</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.2845131824787212</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.086686734482042768</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.17905958065185801</v>
+      </c>
+      <c r="X51" s="8">
+        <v>31.283300000000001</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.6458250000000003</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>6.1666999999999996</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>24.916699999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8734,7 +8840,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>9.6245600000000007</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -10964,7 +11072,9 @@
       <c r="AB76" s="8">
         <v>4.1523138888888891</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>8.3662019999999995</v>
+      </c>
       <c r="AD76" s="8">
         <v>17.313425000000002</v>
       </c>
@@ -14164,7 +14274,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14200,25 +14310,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>1815.3</v>
+      </c>
+      <c r="P102" s="5">
+        <v>1815.3</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.42402147426134629</v>
+      </c>
+      <c r="R102" s="7">
+        <v>23</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33165867900622487</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.11032639233184598</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0673748140803173</v>
+      </c>
+      <c r="X102" s="8">
+        <v>26.36470588235294</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>4.8007590909090903</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>6.1270812499999998</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>11.070220000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>17.290194117647058</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.70588235294117652</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -17040,7 +17186,7 @@
         <v>0.055520139504302332</v>
       </c>
       <c r="W125" s="6">
-        <v>-0.0030878667467101185</v>
+        <v>-0.0015203491419151346</v>
       </c>
       <c r="X125" s="8">
         <v>27.665217391304346</v>
@@ -21433,7 +21579,7 @@
         <v>0.15359241641827343</v>
       </c>
       <c r="W160" s="6">
-        <v>0.048933558819703286</v>
+        <v>0.046303512949440906</v>
       </c>
       <c r="X160" s="8">
         <v>37.657692307692308</v>
@@ -25837,7 +25983,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25873,25 +26019,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>2856.9299999999998</v>
+      </c>
+      <c r="P195" s="5">
+        <v>2856.9299999999998</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>-0.045733754196102039</v>
+      </c>
+      <c r="R195" s="7">
+        <v>37</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.15909090909090906</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.35397374104370777</v>
+      </c>
+      <c r="U195" s="6">
+        <v>0.044984721361741455</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.042020455523936531</v>
+      </c>
+      <c r="W195" s="6">
+        <v>0.0039831217425698217</v>
+      </c>
+      <c r="X195" s="8">
+        <v>22.104627777777779</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>4.0779411764705884</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>4.2666666666666666</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>15.332405555555555</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.94444444444444442</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-341.5</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
